--- a/Document.xlsx
+++ b/Document.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>sl.no</t>
   </si>
@@ -65,37 +65,28 @@
     <t>Data Strategy Version</t>
   </si>
   <si>
-    <t>OVRL_raw</t>
-  </si>
-  <si>
-    <t>SIG_raw</t>
-  </si>
-  <si>
-    <t>BAK_raw</t>
-  </si>
-  <si>
-    <t>OVRL</t>
-  </si>
-  <si>
-    <t>SIG</t>
-  </si>
-  <si>
-    <t>BAK</t>
-  </si>
-  <si>
-    <t>p808 mos</t>
-  </si>
-  <si>
-    <t>SI-SDR</t>
-  </si>
-  <si>
-    <t>WER</t>
-  </si>
-  <si>
-    <t>pesq</t>
-  </si>
-  <si>
-    <t>polqa</t>
+    <t>v1</t>
+  </si>
+  <si>
+    <t>pytorch</t>
+  </si>
+  <si>
+    <t>Model is trained for BVS task with two source predictions i.e., primary speaker speech and remaining speech/noise present in the mix input.</t>
+  </si>
+  <si>
+    <t>Resepformer</t>
+  </si>
+  <si>
+    <t>Resepformer: Resource-Efficient separation transformer model directly operates on audio. Encoder-Masknet-Decoder architecture.</t>
+  </si>
+  <si>
+    <t>3.2G</t>
+  </si>
+  <si>
+    <t>Negative sisnr</t>
+  </si>
+  <si>
+    <t>V6p3 BVS 100hrs data</t>
   </si>
 </sst>
 </file>
@@ -743,7 +734,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -759,11 +750,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1090,7 +1080,7 @@
     <col min="3" max="3" width="11.25" customWidth="1"/>
     <col min="4" max="4" width="38.25" customWidth="1"/>
     <col min="6" max="6" width="22.6296296296296" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="11.25" customWidth="1"/>
     <col min="12" max="12" width="21" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
@@ -1134,49 +1124,52 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" ht="57.6" spans="1:20">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="G2" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="H2" s="4">
+        <v>9.6</v>
+      </c>
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="4:20">
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2"/>
-      <c r="L2"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
@@ -1184,13 +1177,13 @@
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
       <c r="S2" s="8"/>
-      <c r="T2" s="11"/>
+      <c r="T2" s="10"/>
     </row>
     <row r="3" spans="20:20">
-      <c r="T3" s="11"/>
+      <c r="T3" s="10"/>
     </row>
     <row r="4" spans="20:20">
-      <c r="T4" s="11"/>
+      <c r="T4" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
